--- a/examples/06-workbook-features.xlsx
+++ b/examples/06-workbook-features.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fileSharing readOnlyRecommended="1"/>
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
@@ -438,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -462,8 +463,26 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cell B3 can be edited with its own password (range 'Input')</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <protectedRanges>
+    <protectedRange sqref="B3" name="Input" algorithmName="SHA-512" hashValue="Dg5gGu0VbAqKeUzRz6dHo9nJ0mkPzqtNUnvWIBNExmuYrfgjeRUvePjPH8zhL2CrYhhlymzCP9Pyo6EZAwN7Vw==" saltValue="yMNjgUq6n7Hs2cRldfQ+Bg==" spinCount="100000"/>
+  </protectedRanges>
+  <customSheetViews>
+    <customSheetView guid="{3F2504E0-4F89-11D3-9A0C-0305E82C3301}" scale="120" showGridLines="0">
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
+  </customSheetViews>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>

--- a/examples/06-workbook-features.xlsx
+++ b/examples/06-workbook-features.xlsx
@@ -3,18 +3,23 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileSharing readOnlyRecommended="1"/>
   <workbookPr/>
-  <workbookProtection/>
+  <workbookProtection lockStructure="1"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Contacts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Archive" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Internal" sheetId="4" state="veryHidden" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$B$44</definedName>
+    <definedName name="FirstContact" localSheetId="1">Contacts!$A$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -473,8 +478,408 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Line 2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Line 3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Line 4</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Line 5</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Line 6</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Line 7</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Line 8</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Line 9</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Line 10</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Line 11</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Line 12</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Line 13</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Line 14</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Line 15</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Line 16</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Line 17</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Line 18</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Line 19</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Line 20</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Line 21</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Line 22</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Line 23</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Line 24</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Line 25</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Line 26</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Line 27</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Line 28</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Line 29</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Line 30</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Line 31</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Line 32</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Line 33</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Line 34</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Line 36</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Line 37</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Line 38</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Line 39</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Line 40</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
   <protectedRanges>
     <protectedRange sqref="B3" name="Input" algorithmName="SHA-512" hashValue="Dg5gGu0VbAqKeUzRz6dHo9nJ0mkPzqtNUnvWIBNExmuYrfgjeRUvePjPH8zhL2CrYhhlymzCP9Pyo6EZAwN7Vw==" saltValue="yMNjgUq6n7Hs2cRldfQ+Bg==" spinCount="100000"/>
   </protectedRanges>
@@ -483,7 +888,103 @@
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>
   </customSheetViews>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.8" bottom="0.8" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;F — &amp;A&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LConfidential&amp;CPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="24" min="0" max="16383" man="1"/>
+  </rowBreaks>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="1" min="0" max="16383" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Olena</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>+380 44 000 0000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Hidden sheet</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Very hidden: only VBA or the XML can show it</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/examples/06-workbook-features.xlsx
+++ b/examples/06-workbook-features.xlsx
@@ -438,7 +438,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FFC00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -892,7 +892,7 @@
   <pageMargins left="0.5" right="0.5" top="0.8" bottom="0.8" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;F — &amp;A&amp;R&amp;D</oddHeader>
+    <oddHeader>&amp;L&amp;G&amp;C&amp;F — &amp;A&amp;R&amp;D</oddHeader>
     <oddFooter>&amp;LConfidential&amp;CPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -905,11 +905,12 @@
   <colBreaks count="1" manualBreakCount="1">
     <brk id="1" min="0" max="16383" man="1"/>
   </colBreaks>
+  <legacyDrawingHF r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -944,6 +945,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <picture r:id="rId1"/>
 </worksheet>
 </file>
 
